--- a/opportunity_findings.xlsx
+++ b/opportunity_findings.xlsx
@@ -8,14 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" r:id="rId1"/>
-    <sheet name="Contract Expiry Opportunity" sheetId="2" r:id="rId2"/>
+    <sheet name="Maverick Spend Detection" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="35">
   <si>
     <t>detector_type</t>
   </si>
@@ -23,7 +23,7 @@
     <t>financial_impact_gbp</t>
   </si>
   <si>
-    <t>Contract Expiry Opportunity</t>
+    <t>Maverick Spend Detection</t>
   </si>
   <si>
     <t>opportunity_id</t>
@@ -41,15 +41,9 @@
     <t>supplier_name</t>
   </si>
   <si>
-    <t>category_id</t>
-  </si>
-  <si>
     <t>item_id</t>
   </si>
   <si>
-    <t>item_reference</t>
-  </si>
-  <si>
     <t>calculation_details</t>
   </si>
   <si>
@@ -74,67 +68,55 @@
     <t>is_rejected</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>contract_expiry_check_contract_expiry_opportunity_16f98ddc_s_i000852_c01172</t>
-  </si>
-  <si>
-    <t>contract_expiry_check_contract_expiry_opportunity_6dd5147b_s_i001002_c01050</t>
-  </si>
-  <si>
-    <t>contract_expiry_check</t>
-  </si>
-  <si>
-    <t>SI000852</t>
-  </si>
-  <si>
-    <t>SI001002</t>
-  </si>
-  <si>
-    <t>Dixon, Reynolds and Solomon</t>
-  </si>
-  <si>
-    <t>Sarah Thompson</t>
-  </si>
-  <si>
-    <t>IT &amp; Technology</t>
-  </si>
-  <si>
-    <t>Marketing &amp; Media</t>
-  </si>
-  <si>
-    <t>Lenovo ThinkCentre M70t Intel i5, 8GB RAM, 256GB SSD, Win 11 Pro</t>
-  </si>
-  <si>
-    <t>Consulting</t>
-  </si>
-  <si>
-    <t>C01172</t>
-  </si>
-  <si>
-    <t>C01050</t>
-  </si>
-  <si>
-    <t>{'contract_title': 'Synthesize Efficient Niches', 'contract_end_date': '2026-05-10', 'days_to_expiry': 41, 'item_reference': 'C01172', 'item_description': 'Lenova ThinkCentre M70t Intel i5, 8GB RAM, 256GB SSD,', 'catalog_product': 'Lenovo ThinkCentre M70t Intel i5, 8GB RAM, 256GB SSD, Win 11 Pro', 'catalog_categories': {'category_level_1': 'Office &amp; Administrative Supplies', 'category_level_2': 'IT Equipment', 'category_level_3': 'Computers', 'category_level_4': 'Desktops', 'category_level_5': 'Desktop Computers'}, 'risk_score_normalised': 0.0, 'flow_coverage': 1.0}</t>
-  </si>
-  <si>
-    <t>{'contract_title': 'Reinvent Magnetic Metrics', 'contract_end_date': '2026-06-19', 'days_to_expiry': 81, 'item_reference': 'C01050', 'item_description': 'Consulting', 'risk_score_normalised': 0.0, 'flow_coverage': 1.0}</t>
-  </si>
-  <si>
-    <t>['C01172']</t>
-  </si>
-  <si>
-    <t>['C01050']</t>
-  </si>
-  <si>
-    <t>2026-03-30T19:38:06.428823</t>
-  </si>
-  <si>
-    <t>2026-03-30T19:38:03.741503</t>
+    <t>9</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>maverick_spend_check_maverick_spend_detection_1cc91a07_s_u_p_c_i_t_y_o_f_n_e_w_p_o_r_t_na</t>
+  </si>
+  <si>
+    <t>maverick_spend_check_maverick_spend_detection_5f9eb882_s_u_p_t_e_c_h_w_o_r_l_d_na</t>
+  </si>
+  <si>
+    <t>maverick_spend_check</t>
+  </si>
+  <si>
+    <t>SUP-CITYOFNEWPORT</t>
+  </si>
+  <si>
+    <t>SUP-TECHWORLD</t>
+  </si>
+  <si>
+    <t>City of Newport</t>
+  </si>
+  <si>
+    <t>TechWorld</t>
+  </si>
+  <si>
+    <t>Tier 3 Marketing Services (Months 1-10) 3-5 Posts Per Week</t>
+  </si>
+  <si>
+    <t>Full IT Partnership Bundle</t>
+  </si>
+  <si>
+    <t>{'po_total': 100000.0, 'item_description': 'Tier 3 Marketing Services (Months 1-10) 3-5 Posts Per Week', 'risk_score_normalised': 0.0, 'flow_coverage': 1.0}</t>
+  </si>
+  <si>
+    <t>{'po_total': 81000.0, 'item_description': 'Full IT Partnership Bundle', 'risk_score_normalised': 0.0, 'flow_coverage': 1.0}</t>
+  </si>
+  <si>
+    <t>['502004']</t>
+  </si>
+  <si>
+    <t>['405867']</t>
+  </si>
+  <si>
+    <t>2026-06-08T18:49:24.842477</t>
+  </si>
+  <si>
+    <t>2026-06-08T18:49:24.843933</t>
   </si>
   <si>
     <t>[]</t>
@@ -485,7 +467,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>1721012.44</v>
+        <v>181000</v>
       </c>
     </row>
   </sheetData>
@@ -495,10 +477,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:16">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -521,13 +503,13 @@
         <v>8</v>
       </c>
       <c r="H1" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" t="s">
         <v>9</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>10</v>
-      </c>
-      <c r="J1" t="s">
-        <v>1</v>
       </c>
       <c r="K1" t="s">
         <v>11</v>
@@ -547,122 +529,104 @@
       <c r="P1" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" t="s">
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" t="s">
         <v>17</v>
       </c>
-      <c r="R1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>19</v>
-      </c>
-      <c r="B2" t="s">
-        <v>21</v>
       </c>
       <c r="C2" t="s">
         <v>2</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" t="s">
         <v>24</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>26</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2">
+        <v>100000</v>
+      </c>
+      <c r="I2" t="s">
         <v>28</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>30</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>32</v>
       </c>
-      <c r="J2">
-        <v>998645.86</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="L2">
+        <v>0.5524861878453039</v>
+      </c>
+      <c r="M2" t="s">
         <v>34</v>
       </c>
-      <c r="L2" t="s">
-        <v>36</v>
-      </c>
-      <c r="M2" t="s">
-        <v>38</v>
-      </c>
-      <c r="N2">
-        <v>0.5802664970858665</v>
-      </c>
-      <c r="O2" t="s">
-        <v>40</v>
-      </c>
-      <c r="P2" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q2">
+      <c r="N2" t="s">
+        <v>34</v>
+      </c>
+      <c r="O2">
         <v>1</v>
       </c>
-      <c r="R2" t="b">
+      <c r="P2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:16">
       <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
         <v>20</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
       </c>
       <c r="C3" t="s">
         <v>2</v>
       </c>
       <c r="D3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
         <v>23</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>25</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>27</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3">
+        <v>81000</v>
+      </c>
+      <c r="I3" t="s">
         <v>29</v>
       </c>
-      <c r="H3" t="s">
+      <c r="J3" t="s">
         <v>31</v>
       </c>
-      <c r="I3" t="s">
+      <c r="K3" t="s">
         <v>33</v>
       </c>
-      <c r="J3">
-        <v>722366.58</v>
-      </c>
-      <c r="K3" t="s">
-        <v>35</v>
-      </c>
-      <c r="L3" t="s">
-        <v>37</v>
+      <c r="L3">
+        <v>0.4475138121546962</v>
       </c>
       <c r="M3" t="s">
-        <v>39</v>
-      </c>
-      <c r="N3">
-        <v>0.4197335029141335</v>
-      </c>
-      <c r="O3" t="s">
-        <v>40</v>
-      </c>
-      <c r="P3" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q3">
+        <v>34</v>
+      </c>
+      <c r="N3" t="s">
+        <v>34</v>
+      </c>
+      <c r="O3">
         <v>0</v>
       </c>
-      <c r="R3" t="b">
+      <c r="P3" t="b">
         <v>0</v>
       </c>
     </row>
